--- a/exports/sample_result.xlsx
+++ b/exports/sample_result.xlsx
@@ -7,11 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings Used" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tariffs Snapshot" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Warnings" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Результат" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Параметры" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Что проверить" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -70,13 +69,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -443,273 +442,261 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO4"/>
+  <dimension ref="A1:AM4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="27" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="22" customWidth="1" min="21" max="21"/>
-    <col width="24" customWidth="1" min="22" max="22"/>
-    <col width="23" customWidth="1" min="23" max="23"/>
-    <col width="17" customWidth="1" min="24" max="24"/>
-    <col width="22" customWidth="1" min="25" max="25"/>
-    <col width="25" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
-    <col width="12" customWidth="1" min="28" max="28"/>
-    <col width="17" customWidth="1" min="29" max="29"/>
-    <col width="16" customWidth="1" min="30" max="30"/>
-    <col width="20" customWidth="1" min="31" max="31"/>
-    <col width="13" customWidth="1" min="32" max="32"/>
-    <col width="26" customWidth="1" min="33" max="33"/>
-    <col width="19" customWidth="1" min="34" max="34"/>
-    <col width="16" customWidth="1" min="35" max="35"/>
+    <col width="17" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="19" customWidth="1" min="25" max="25"/>
+    <col width="24" customWidth="1" min="26" max="26"/>
+    <col width="17" customWidth="1" min="27" max="27"/>
+    <col width="23" customWidth="1" min="28" max="28"/>
+    <col width="24" customWidth="1" min="29" max="29"/>
+    <col width="15" customWidth="1" min="30" max="30"/>
+    <col width="19" customWidth="1" min="31" max="31"/>
+    <col width="18" customWidth="1" min="32" max="32"/>
+    <col width="30" customWidth="1" min="33" max="33"/>
+    <col width="30" customWidth="1" min="34" max="34"/>
+    <col width="17" customWidth="1" min="35" max="35"/>
     <col width="12" customWidth="1" min="36" max="36"/>
-    <col width="12" customWidth="1" min="37" max="37"/>
-    <col width="23" customWidth="1" min="38" max="38"/>
-    <col width="28" customWidth="1" min="39" max="39"/>
-    <col width="27" customWidth="1" min="40" max="40"/>
-    <col width="28" customWidth="1" min="41" max="41"/>
+    <col width="20" customWidth="1" min="37" max="37"/>
+    <col width="25" customWidth="1" min="38" max="38"/>
+    <col width="13" customWidth="1" min="39" max="39"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>Артикул</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Product Name</t>
+          <t>Название товара</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Модель</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Категория</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Category Source</t>
+          <t>Источник категории</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Commission Rate %</t>
+          <t>Комиссия, %</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Commission Rate Status</t>
+          <t>Себестоимость, ₽</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Current Price RUB</t>
+          <t>Вес, кг</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Target Margin %</t>
+          <t>Длина, см</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Cost RUB</t>
+          <t>Ширина, см</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Weight kg</t>
+          <t>Высота, см</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Length cm</t>
+          <t>Объем, л</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Width cm</t>
+          <t>Объемный вес, кг</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Height cm</t>
+          <t>Сумма сторон, см</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Volume liters</t>
+          <t>КГТ</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Volumetric weight kg</t>
+          <t>Целевая маржинальность, %</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Sum sides cm</t>
+          <t>Налоговая система</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Is KGT</t>
+          <t>Налог, %</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Expected Revenue RUB</t>
+          <t>Выкупаемость, %</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Commission RUB</t>
+          <t>Реклама, %</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Payment Transfer RUB</t>
+          <t>Брак / потери, %</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Payment Acceptance RUB</t>
+          <t>Ожидаемая выручка, ₽</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Delivery to Buyer RUB</t>
+          <t>Комиссия ЯМ, ₽</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Middle Mile RUB</t>
+          <t>Перевод платежей, ₽</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Reverse Handling RUB</t>
+          <t>Прием платежей, ₽</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Reverse Middle Mile RUB</t>
+          <t>Доставка покупателю, ₽</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Tax RUB</t>
+          <t>Средняя миля, ₽</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Ads RUB</t>
+          <t>Обратная логистика, ₽</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Defect Cost RUB</t>
+          <t>Обработка возвратов, ₽</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>FBS Pickup RUB</t>
+          <t>FBS: забор, ₽</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>FBS Processing RUB</t>
+          <t>FBS: обработка, ₽</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Storage RUB</t>
+          <t>FBY: хранение, ₽</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Inbound to Yandex WH RUB</t>
+          <t>FBY: доставка до склада ЯМ, ₽</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Expected COGS RUB</t>
+          <t>Ожидаемая себестоимость проданных товаров, ₽</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Total Cost RUB</t>
+          <t>Итого затрат, ₽</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>Profit RUB</t>
+          <t>Прибыль, ₽</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>Margin %</t>
+          <t>Маржа, % к выручке</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>Recommended Price RUB</t>
+          <t>Рекомендованная цена, ₽</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>Recommended Price Delta RUB</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>Recommended Price Delta %</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
+          <t>Комментарий</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>YM-001</t>
+          <t>TSRD00175588</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Горный велосипед 27.5 алюминий</t>
+          <t>Велосипед горный взрослый 29 дюймов</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>FBY</t>
+          <t>FBS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -719,131 +706,123 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>keyword:велосипед</t>
+          <t>по ключевому слову: велосипед</t>
         </is>
       </c>
       <c r="F2" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>32990</v>
-      </c>
-      <c r="I2" s="3" t="n">
+      <c r="G2" s="4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="J2" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="J2" s="4" t="n">
-        <v>21500</v>
-      </c>
       <c r="K2" s="2" t="n">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>140</v>
+        <v>224</v>
       </c>
       <c r="M2" s="2" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="N2" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="O2" s="2" t="n">
-        <v>224</v>
-      </c>
-      <c r="P2" s="2" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="Q2" s="2" t="n">
-        <v>240</v>
-      </c>
-      <c r="R2" s="2" t="b">
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>УСН 6%</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="U2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="S2" s="4" t="n">
-        <v>31340.5</v>
-      </c>
-      <c r="T2" s="4" t="n">
-        <v>1567.02</v>
-      </c>
-      <c r="U2" s="4" t="n">
-        <v>720.83</v>
-      </c>
       <c r="V2" s="4" t="n">
+        <v>33635.86</v>
+      </c>
+      <c r="W2" s="4" t="n">
+        <v>1681.79</v>
+      </c>
+      <c r="X2" s="4" t="n">
+        <v>773.62</v>
+      </c>
+      <c r="Y2" s="4" t="n">
         <v>0.12</v>
       </c>
-      <c r="W2" s="4" t="n">
+      <c r="Z2" s="4" t="n">
         <v>1000</v>
       </c>
-      <c r="X2" s="4" t="n">
+      <c r="AA2" s="4" t="n">
         <v>3696</v>
       </c>
-      <c r="Y2" s="4" t="n">
+      <c r="AB2" s="4" t="n">
+        <v>184.8</v>
+      </c>
+      <c r="AC2" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="Z2" s="4" t="n">
-        <v>184.8</v>
-      </c>
-      <c r="AA2" s="4" t="n">
-        <v>1880.43</v>
-      </c>
-      <c r="AB2" s="4" t="n">
-        <v>2507.24</v>
-      </c>
-      <c r="AC2" s="4" t="n">
-        <v>215</v>
-      </c>
       <c r="AD2" s="4" t="n">
-        <v>0</v>
+        <v>14.58</v>
       </c>
       <c r="AE2" s="4" t="n">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="AF2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AG2" s="4" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AH2" s="4" t="n">
-        <v>20425</v>
+        <v>14250</v>
       </c>
       <c r="AI2" s="4" t="n">
-        <v>32347.2</v>
+        <v>26908.69</v>
       </c>
       <c r="AJ2" s="4" t="n">
-        <v>-1006.7</v>
+        <v>6727.17</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>-3.21</v>
+        <v>20</v>
       </c>
       <c r="AL2" s="4" t="n">
-        <v>46035.45</v>
-      </c>
-      <c r="AM2" s="4" t="n">
-        <v>13045.45</v>
-      </c>
-      <c r="AN2" s="3" t="n">
-        <v>39.54</v>
-      </c>
-      <c r="AO2" s="2" t="inlineStr">
-        <is>
-          <t>пример FBY, наша доставка до склада ЯМ задана по строке</t>
-        </is>
-      </c>
+        <v>35406.17</v>
+      </c>
+      <c r="AM2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>YM-002</t>
+          <t>DRL000245</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Дрель ударная 810Вт</t>
+          <t>Дрель ударная с кейсом 800 Вт</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -858,82 +837,84 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>keyword:дрель</t>
+          <t>по ключевому слову: дрель</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>5490</v>
-      </c>
-      <c r="I3" s="3" t="n">
+      <c r="G3" s="4" t="n">
+        <v>3500</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="J3" s="4" t="n">
-        <v>3100</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="N3" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="O3" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q3" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="R3" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S3" s="4" t="n">
-        <v>5215.5</v>
-      </c>
-      <c r="T3" s="4" t="n">
-        <v>365.08</v>
-      </c>
-      <c r="U3" s="4" t="n">
-        <v>119.96</v>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>УСН 6%</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="V3" s="4" t="n">
+        <v>7105</v>
+      </c>
+      <c r="W3" s="4" t="n">
+        <v>497.35</v>
+      </c>
+      <c r="X3" s="4" t="n">
+        <v>163.42</v>
+      </c>
+      <c r="Y3" s="4" t="n">
         <v>0.12</v>
       </c>
-      <c r="W3" s="4" t="n">
-        <v>274.5</v>
-      </c>
-      <c r="X3" s="4" t="n">
+      <c r="Z3" s="4" t="n">
+        <v>373.95</v>
+      </c>
+      <c r="AA3" s="4" t="n">
         <v>246</v>
       </c>
-      <c r="Y3" s="4" t="n">
+      <c r="AB3" s="4" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="AC3" s="4" t="n">
         <v>0.75</v>
-      </c>
-      <c r="Z3" s="4" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="AA3" s="4" t="n">
-        <v>312.93</v>
-      </c>
-      <c r="AB3" s="4" t="n">
-        <v>417.24</v>
-      </c>
-      <c r="AC3" s="4" t="n">
-        <v>31</v>
       </c>
       <c r="AD3" s="4" t="n">
         <v>14.58</v>
@@ -948,41 +929,31 @@
         <v>0</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>2945</v>
+        <v>3325</v>
       </c>
       <c r="AI3" s="4" t="n">
-        <v>4760.3</v>
+        <v>5684</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>455.2</v>
+        <v>1421</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>8.73</v>
+        <v>20</v>
       </c>
       <c r="AL3" s="4" t="n">
-        <v>6693.11</v>
-      </c>
-      <c r="AM3" s="4" t="n">
-        <v>1203.11</v>
-      </c>
-      <c r="AN3" s="3" t="n">
-        <v>21.91</v>
-      </c>
-      <c r="AO3" s="2" t="inlineStr">
-        <is>
-          <t>пример FBS</t>
-        </is>
-      </c>
+        <v>7478.95</v>
+      </c>
+      <c r="AM3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>YM-003</t>
+          <t>SMX1001</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Смеситель для ванной латунь</t>
+          <t>Смеситель для кухни хром</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -997,82 +968,84 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>keyword:смеситель</t>
+          <t>по ключевому слову: смеситель</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>7990</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>4200</v>
+      <c r="G4" s="4" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>22</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1.8</v>
+        <v>8</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>18</v>
+        <v>1.41</v>
       </c>
       <c r="N4" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>УСН 6%</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="T4" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="Q4" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="R4" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" s="4" t="n">
-        <v>7590.5</v>
-      </c>
-      <c r="T4" s="4" t="n">
-        <v>607.24</v>
-      </c>
-      <c r="U4" s="4" t="n">
-        <v>174.58</v>
+      <c r="U4" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="V4" s="4" t="n">
+        <v>3964.34</v>
+      </c>
+      <c r="W4" s="4" t="n">
+        <v>317.15</v>
+      </c>
+      <c r="X4" s="4" t="n">
+        <v>91.18000000000001</v>
+      </c>
+      <c r="Y4" s="4" t="n">
         <v>0.12</v>
       </c>
-      <c r="W4" s="4" t="n">
-        <v>399.5</v>
-      </c>
-      <c r="X4" s="4" t="n">
-        <v>158</v>
-      </c>
-      <c r="Y4" s="4" t="n">
+      <c r="Z4" s="4" t="n">
+        <v>208.65</v>
+      </c>
+      <c r="AA4" s="4" t="n">
+        <v>224</v>
+      </c>
+      <c r="AB4" s="4" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="AC4" s="4" t="n">
         <v>0.75</v>
-      </c>
-      <c r="Z4" s="4" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AA4" s="4" t="n">
-        <v>455.43</v>
-      </c>
-      <c r="AB4" s="4" t="n">
-        <v>607.24</v>
-      </c>
-      <c r="AC4" s="4" t="n">
-        <v>42</v>
       </c>
       <c r="AD4" s="4" t="n">
         <v>14.58</v>
@@ -1087,31 +1060,21 @@
         <v>0</v>
       </c>
       <c r="AH4" s="4" t="n">
-        <v>3990</v>
+        <v>1710</v>
       </c>
       <c r="AI4" s="4" t="n">
-        <v>6478.18</v>
+        <v>3171.47</v>
       </c>
       <c r="AJ4" s="4" t="n">
-        <v>1112.32</v>
+        <v>792.87</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>14.65</v>
+        <v>20</v>
       </c>
       <c r="AL4" s="4" t="n">
-        <v>9598.07</v>
-      </c>
-      <c r="AM4" s="4" t="n">
-        <v>1608.07</v>
-      </c>
-      <c r="AN4" s="3" t="n">
-        <v>20.13</v>
-      </c>
-      <c r="AO4" s="2" t="inlineStr">
-        <is>
-          <t>пример с target margin override</t>
-        </is>
-      </c>
+        <v>4172.99</v>
+      </c>
+      <c r="AM4" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1124,29 +1087,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>parameter</t>
+          <t>Параметр</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>Значение</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>default_model</t>
+          <t>Модель</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -1158,37 +1121,39 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>target_margin_pct</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>20</v>
+          <t>Налоговая система</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>УСН 6%</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>buyout_rate_pct</t>
+          <t>Целевая маржинальность, %</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>95</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>tax_rate_pct</t>
+          <t>Выкупаемость, %</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>6</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ad_rate_pct</t>
+          <t>Реклама, %</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -1198,7 +1163,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>defect_rate_pct</t>
+          <t>Брак / потери, %</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1208,49 +1173,47 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>transfer_schedule</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Еженедельно, с отсрочкой в 2 недели</t>
-        </is>
+          <t>Возвраты без обратной средней мили, %</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>reverse_same_locality_share_pct</t>
+          <t>FBS: среднее число заказов в день</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>fbs_avg_orders_per_day</t>
+          <t>Среднее число товаров в заказе</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>20</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>avg_items_per_order</t>
+          <t>FBY: срок хранения, дней</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1.2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>fby_storage_cost_rub_per_unit</t>
+          <t>FBY: хранение, ₽ в день за 1 шт.</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1260,41 +1223,11 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>fby_inbound_self_delivery_rub_per_unit</t>
+          <t>FBY: наша доставка до склада ЯМ, ₽/шт.</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>default_commission_rate_pct</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>kgt_weight_threshold_kg</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>kgt_sum_sides_threshold_cm</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -1308,259 +1241,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>parameter</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
+          <t>Статус</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>delivery_to_buyer_rate_pct</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>delivery_to_buyer_cap_rub</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>middle_mile_base_rub</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>middle_mile_up_to_160_rub_per_l</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>middle_mile_over_160_rub_per_l</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>payment_acceptance_rub_per_sku</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>returns_handling_rub_per_shipment</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>fbs_regular_processing_rub_per_order</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>fbs_kgt_processing_rub_per_kg</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>fbs_return_free_storage_days</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>fbs_return_storage_rub_per_day</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>fby_storage_after_365_apparel_rub_per_l</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>fby_storage_after_365_other_rub_per_l</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>fby_excess_intake_rub</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>fby_remove_small_rub</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>fby_remove_large_rub</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>fby_dispose_small_rub</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>fby_dispose_large_rub</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>payment_transfer_schedule</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>rate_pct</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Еженедельно, с отсрочкой в 4 недели</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Еженедельно, с отсрочкой в 2 недели</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Еженедельно, с отсрочкой в 1 неделю</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Ежедневно</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>3.3</v>
+          <t>Замечаний нет</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1574,48 +1272,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Info</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Без предупреждений</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Название</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -1663,7 +1330,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Калькулятор дохода</t>
+          <t>Калькулятор Яндекс Маркета</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">

--- a/exports/sample_result.xlsx
+++ b/exports/sample_result.xlsx
@@ -1,81 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Результат" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Параметры" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Что проверить" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t>Артикул</t>
-  </si>
-  <si>
-    <t>Название товара</t>
-  </si>
-  <si>
-    <t>Себестоимость</t>
-  </si>
-  <si>
-    <t>Комиссия</t>
-  </si>
-  <si>
-    <t>Логистика</t>
-  </si>
-  <si>
-    <t>Эквайринг</t>
-  </si>
-  <si>
-    <t>Полная себестоимость</t>
-  </si>
-  <si>
-    <t>Рекомендованная цена</t>
-  </si>
-  <si>
-    <t>Маржа %</t>
-  </si>
-  <si>
-    <t>TEST-1</t>
-  </si>
-  <si>
-    <t>Пример товар</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -87,35 +55,101 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="00D9E2F3"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -403,69 +437,909 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AM4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="27" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="17" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="19" customWidth="1" min="25" max="25"/>
+    <col width="24" customWidth="1" min="26" max="26"/>
+    <col width="17" customWidth="1" min="27" max="27"/>
+    <col width="23" customWidth="1" min="28" max="28"/>
+    <col width="24" customWidth="1" min="29" max="29"/>
+    <col width="15" customWidth="1" min="30" max="30"/>
+    <col width="19" customWidth="1" min="31" max="31"/>
+    <col width="18" customWidth="1" min="32" max="32"/>
+    <col width="30" customWidth="1" min="33" max="33"/>
+    <col width="30" customWidth="1" min="34" max="34"/>
+    <col width="17" customWidth="1" min="35" max="35"/>
+    <col width="12" customWidth="1" min="36" max="36"/>
+    <col width="20" customWidth="1" min="37" max="37"/>
+    <col width="25" customWidth="1" min="38" max="38"/>
+    <col width="13" customWidth="1" min="39" max="39"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Артикул</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Название товара</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Модель</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Категория</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Источник категории</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Комиссия, %</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Себестоимость, ₽</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Вес, кг</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Длина, см</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Ширина, см</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Высота, см</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Объем, л</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Объемный вес, кг</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Сумма сторон, см</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>КГТ</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Целевая маржинальность, %</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Налоговая система</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Налог, %</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Выкупаемость, %</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Реклама, %</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Брак / потери, %</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Ожидаемая выручка, ₽</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Комиссия ЯМ, ₽</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Перевод платежей, ₽</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Прием платежей, ₽</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Доставка покупателю, ₽</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Средняя миля, ₽</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Обратная логистика, ₽</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Обработка возвратов, ₽</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>FBS: забор, ₽</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>FBS: обработка, ₽</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>FBY: хранение, ₽</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>FBY: доставка до склада ЯМ, ₽</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Ожидаемая себестоимость проданных товаров, ₽</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Итого затрат, ₽</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Прибыль, ₽</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Маржа, % к выручке</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Рекомендованная цена, ₽</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>TSRD00175588</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Велосипед горный взрослый 29 дюймов</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>FBS</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Велосипеды</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>по ключевому слову: велосипед</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>224</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>УСН 6%</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" s="4" t="n">
+        <v>33635.86</v>
+      </c>
+      <c r="W2" s="4" t="n">
+        <v>1681.79</v>
+      </c>
+      <c r="X2" s="4" t="n">
+        <v>773.62</v>
+      </c>
+      <c r="Y2" s="4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="Z2" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" s="4" t="n">
+        <v>3696</v>
+      </c>
+      <c r="AB2" s="4" t="n">
+        <v>184.8</v>
+      </c>
+      <c r="AC2" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AD2" s="4" t="n">
+        <v>14.58</v>
+      </c>
+      <c r="AE2" s="4" t="n">
+        <v>448</v>
+      </c>
+      <c r="AF2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="AG2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="4" t="n">
+        <v>14250</v>
+      </c>
+      <c r="AI2" s="4" t="n">
+        <v>26908.69</v>
+      </c>
+      <c r="AJ2" s="4" t="n">
+        <v>6727.17</v>
+      </c>
+      <c r="AK2" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL2" s="4" t="n">
+        <v>35406.17</v>
+      </c>
+      <c r="AM2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>DRL000245</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Дрель ударная с кейсом 800 Вт</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>FBS</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Электроинструмент</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>по ключевому слову: дрель</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>3500</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>УСН 6%</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="U3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="V3" s="4" t="n">
+        <v>7105</v>
+      </c>
+      <c r="W3" s="4" t="n">
+        <v>497.35</v>
+      </c>
+      <c r="X3" s="4" t="n">
+        <v>163.42</v>
+      </c>
+      <c r="Y3" s="4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="Z3" s="4" t="n">
+        <v>373.95</v>
+      </c>
+      <c r="AA3" s="4" t="n">
+        <v>246</v>
+      </c>
+      <c r="AB3" s="4" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="AC3" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AD3" s="4" t="n">
+        <v>14.58</v>
+      </c>
+      <c r="AE3" s="4" t="n">
+        <v>20.83</v>
+      </c>
+      <c r="AF3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="4" t="n">
+        <v>3325</v>
+      </c>
+      <c r="AI3" s="4" t="n">
+        <v>5684</v>
+      </c>
+      <c r="AJ3" s="4" t="n">
+        <v>1421</v>
+      </c>
+      <c r="AK3" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL3" s="4" t="n">
+        <v>7478.95</v>
+      </c>
+      <c r="AM3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SMX1001</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Смеситель для кухни хром</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>FBS</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Сантехника</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>по ключевому слову: смеситель</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>УСН 6%</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="S4" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="T4" s="3" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2">
-        <v>1000</v>
-      </c>
-      <c r="D2">
-        <v>80</v>
-      </c>
-      <c r="E2">
-        <v>120</v>
-      </c>
-      <c r="F2">
+      <c r="U4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>3964.34</v>
+      </c>
+      <c r="W4" s="4" t="n">
+        <v>317.15</v>
+      </c>
+      <c r="X4" s="4" t="n">
+        <v>91.18000000000001</v>
+      </c>
+      <c r="Y4" s="4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="Z4" s="4" t="n">
+        <v>208.65</v>
+      </c>
+      <c r="AA4" s="4" t="n">
+        <v>224</v>
+      </c>
+      <c r="AB4" s="4" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="AC4" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AD4" s="4" t="n">
+        <v>14.58</v>
+      </c>
+      <c r="AE4" s="4" t="n">
+        <v>20.83</v>
+      </c>
+      <c r="AF4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="4" t="n">
+        <v>1710</v>
+      </c>
+      <c r="AI4" s="4" t="n">
+        <v>3171.47</v>
+      </c>
+      <c r="AJ4" s="4" t="n">
+        <v>792.87</v>
+      </c>
+      <c r="AK4" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="G2">
-        <v>1220</v>
-      </c>
-      <c r="H2">
-        <v>1586</v>
-      </c>
-      <c r="I2">
+      <c r="AL4" s="4" t="n">
+        <v>4172.99</v>
+      </c>
+      <c r="AM4" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Параметр</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Модель</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>FBS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Налоговая система</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>УСН 6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Целевая маржинальность, %</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Выкупаемость, %</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Реклама, %</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Брак / потери, %</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Возвраты без обратной средней мили, %</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>FBS: среднее число заказов в день</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Среднее число товаров в заказе</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>FBY: срок хранения, дней</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
         <v>30</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>FBY: хранение, ₽ в день за 1 шт.</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>FBY: наша доставка до склада ЯМ, ₽/шт.</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Замечаний нет</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Название</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Тарифы FBS</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>https://yandex.ru/support/marketplace/ru/introduction/rates/models/fbs</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Тарифы FBY</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>https://yandex.ru/support/marketplace/ru/introduction/rates/models/fby</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Прием и перевод платежей</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://yandex.ru/support/marketplace/ru/introduction/rates/acquiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Калькулятор Яндекс Маркета</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>https://partner.market.yandex.ru/welcome/cost-calculator</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>